--- a/src/test/resources/TestDriver/Hearst_DSH/ActivityData/DSH_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_DSH/ActivityData/DSH_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +518,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +543,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +568,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +593,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_CAN_New_25</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +623,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_CAN_New_25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,6 +653,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -618,6 +678,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_CAN_Renew_45</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,6 +708,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_CAN_Renew_45</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,6 +738,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +763,16 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_GIFT_US_2999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -698,6 +793,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_GIFT_US_2999</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -718,6 +823,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -738,6 +848,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_MGRT_CAN_Renew_45</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +878,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_MGRT_CAN_Renew_45</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -778,6 +908,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,6 +933,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_MGRT_US_Renew_35</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -818,6 +963,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_MGRT_US_Renew_35</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -838,6 +993,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -858,6 +1018,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_11</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -878,6 +1048,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -898,6 +1078,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -918,6 +1103,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -938,6 +1133,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -958,6 +1163,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -978,6 +1188,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_15</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -998,6 +1218,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_15</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1248,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1038,6 +1273,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_1999</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1058,6 +1303,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_1999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1078,6 +1333,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1098,6 +1358,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_2499</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1118,6 +1388,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_2499</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1138,6 +1418,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1158,6 +1443,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1178,6 +1473,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1503,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1218,6 +1528,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1238,6 +1558,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1258,6 +1588,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1278,6 +1613,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1298,6 +1643,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1318,6 +1673,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1338,6 +1698,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_Renew_3499</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1358,6 +1728,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_Renew_3499</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1378,6 +1758,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1398,6 +1783,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_Renew_35</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1418,6 +1813,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DSH_PRTDIG_US_Renew_35</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1438,6 +1843,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1456,6 +1866,11 @@
       <c r="D52" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
